--- a/data/processed/positivacao/2022-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B940" t="inlineStr"/>
@@ -36297,7 +36297,7 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr"/>
@@ -65371,7 +65371,7 @@
     <row r="2503">
       <c r="A2503" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2503" t="inlineStr"/>
@@ -67042,12 +67042,12 @@
       <c r="A2568" t="inlineStr"/>
       <c r="B2568" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 12 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 12.955,69
+          <t>Vendedor 1 - VENDEDOR 01: positivou 12 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 12.955,69
 Vendedor 18 - LOJA: positivou 60 cliente(s), não positivou 771 cliente(s) - Total vendido: R$ 53.517,18
-Vendedor 3 - FERNANDA: positivou 100 cliente(s), não positivou 343 cliente(s) - Total vendido: R$ 88.927,19
-Vendedor 4 - DANIELA: positivou 32 cliente(s), não positivou 633 cliente(s) - Total vendido: R$ 12.879,51
+Vendedor 3 - VENDEDOR 03: positivou 100 cliente(s), não positivou 343 cliente(s) - Total vendido: R$ 88.927,19
+Vendedor 4 - VENDEDOR 04: positivou 32 cliente(s), não positivou 633 cliente(s) - Total vendido: R$ 12.879,51
 Vendedor 5 - SITE: positivou 9 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 1.084,70
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2568" t="inlineStr"/>
